--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -988,22 +988,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>7.32</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1020,22 +1023,25 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>84.44</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>15.56</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1052,22 +1058,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.56</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.5</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1084,22 +1093,25 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1116,22 +1128,25 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>12.82</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1148,22 +1163,25 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1180,22 +1198,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1212,22 +1233,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1244,22 +1268,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1276,22 +1303,25 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1308,22 +1338,25 @@
         <v>45</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1340,22 +1373,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1424,19 +1460,19 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1459,19 +1495,19 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>93.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3" s="1">
-        <v>6.67</v>
+        <v>11.11</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1506,7 +1542,7 @@
         <v>2.56</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1541,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1564,19 +1600,19 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>94.87</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>5.13</v>
+        <v>12.82</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1611,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1646,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1681,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1716,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1751,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1774,19 +1810,19 @@
         <v>45</v>
       </c>
       <c r="E12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H12" s="1">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1821,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -1023,25 +1023,25 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>84.44</v>
+        <v>86.67</v>
       </c>
       <c r="H3" s="1">
-        <v>15.56</v>
+        <v>13.33</v>
       </c>
       <c r="I3" s="2">
         <v>6.8</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>6.67</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1338,25 +1338,25 @@
         <v>45</v>
       </c>
       <c r="E12">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H12" s="1">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>8.890000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1495,16 +1495,16 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H3" s="1">
-        <v>11.11</v>
+        <v>13.33</v>
       </c>
       <c r="I3" s="2">
         <v>7.4</v>
@@ -1810,16 +1810,16 @@
         <v>45</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H12" s="1">
-        <v>11.11</v>
+        <v>13.33</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -598,13 +598,13 @@
         <v>2.56</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1073,10 +1073,10 @@
         <v>6.5</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1542,13 +1542,13 @@
         <v>2.56</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -668,13 +668,13 @@
         <v>5.13</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1143,10 +1143,10 @@
         <v>8.1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1612,13 +1612,13 @@
         <v>12.82</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -566,10 +566,10 @@
         <v>7.6</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1035,13 +1035,13 @@
         <v>13.33</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1507,13 +1507,13 @@
         <v>13.33</v>
       </c>
       <c r="I3" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1775,19 +1775,19 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -1460,19 +1460,19 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>92.68000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H2" s="1">
-        <v>7.32</v>
+        <v>12.2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1495,19 +1495,19 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H3" s="1">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="I3" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1810,19 +1810,19 @@
         <v>45</v>
       </c>
       <c r="E12">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>86.67</v>
+        <v>84.44</v>
       </c>
       <c r="H12" s="1">
-        <v>13.33</v>
+        <v>15.56</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -1530,16 +1530,16 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>97.44</v>
+        <v>92.31</v>
       </c>
       <c r="H4" s="1">
-        <v>2.56</v>
+        <v>7.69</v>
       </c>
       <c r="I4" s="2">
         <v>7.5</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20221.xlsx
@@ -1600,19 +1600,19 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>0</v>
